--- a/강아지 입양 여부- 문제.xlsx
+++ b/강아지 입양 여부- 문제.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="52">
   <si>
     <t xml:space="preserve">아래의 표는 각각의 조건이 주어졌을 때 강아지 입양 여부 테이블 입니다. </t>
   </si>
@@ -157,9 +157,6 @@
   </si>
   <si>
     <t xml:space="preserve">5. 아래와 같이 X라는 사람의 조건이 주어졌을 때 P(X|강아지 입양 여부 = yes, no)인 확률을 구하시오(위에 확률들 참고해서 작성)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">X =(주거지 = 김해, 수입 = medium, 성별 = 남자, 신용등급=fair) </t>
   </si>
   <si>
     <t xml:space="preserve">답  (yes)         :       </t>
@@ -479,7 +476,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:AS91"/>
-  <sheetFormatPr defaultColWidth="8.609375" defaultRowHeight="16.5" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6015625" defaultRowHeight="16.5" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="13.37"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="11.5"/>
@@ -1352,7 +1349,7 @@
     </row>
     <row r="69" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="12" t="s">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="B69" s="12"/>
       <c r="C69" s="12"/>
@@ -1363,19 +1360,19 @@
     </row>
     <row r="71" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B71" s="17"/>
     </row>
     <row r="72" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="10" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B72" s="17"/>
     </row>
     <row r="75" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1390,7 +1387,7 @@
     </row>
     <row r="77" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="10" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B77" s="17"/>
       <c r="H77" s="4" t="s">
@@ -1414,7 +1411,7 @@
     </row>
     <row r="78" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="10" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B78" s="17"/>
       <c r="H78" s="6" t="n">
@@ -1478,7 +1475,7 @@
     </row>
     <row r="81" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="10" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H81" s="6" t="n">
         <v>4</v>
@@ -1501,7 +1498,7 @@
     </row>
     <row r="82" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="10" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B82" s="17"/>
       <c r="H82" s="6" t="n">
@@ -1720,7 +1717,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="8.609375" defaultRowHeight="16.5" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6015625" defaultRowHeight="16.5" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
@@ -1738,7 +1735,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="8.609375" defaultRowHeight="16.5" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6015625" defaultRowHeight="16.5" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
